--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46349,6 +46349,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2000">
+      <c r="A2000" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2000" t="n">
+        <v>16747</v>
+      </c>
+      <c r="C2000" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="E2000" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="G2000" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46372,6 +46372,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2001">
+      <c r="A2001" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2001" t="n">
+        <v>3746</v>
+      </c>
+      <c r="C2001" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="F2001" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="G2001" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46395,6 +46395,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2002">
+      <c r="A2002" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2002" t="n">
+        <v>4031</v>
+      </c>
+      <c r="C2002" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="G2002" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46418,6 +46418,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2003">
+      <c r="A2003" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2003" t="n">
+        <v>3931</v>
+      </c>
+      <c r="C2003" t="n">
+        <v>14.6499996185303</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G2003" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46259,22 +46259,22 @@
     </row>
     <row r="1996">
       <c r="A1996" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1996" t="n">
-        <v>1285</v>
+        <v>770</v>
       </c>
       <c r="C1996" t="n">
-        <v>13.8000001907349</v>
+        <v>13.6499996185303</v>
       </c>
       <c r="D1996" t="n">
-        <v>13.6000003814697</v>
+        <v>13.5</v>
       </c>
       <c r="E1996" t="n">
-        <v>13.8000001907349</v>
+        <v>13.5</v>
       </c>
       <c r="F1996" t="n">
-        <v>13.8000001907349</v>
+        <v>13.6499996185303</v>
       </c>
       <c r="G1996" t="s">
         <v>7</v>
@@ -46282,22 +46282,22 @@
     </row>
     <row r="1997">
       <c r="A1997" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1997" t="n">
-        <v>2905</v>
+        <v>1285</v>
       </c>
       <c r="C1997" t="n">
-        <v>14.1000003814697</v>
+        <v>13.8000001907349</v>
       </c>
       <c r="D1997" t="n">
-        <v>13.8999996185303</v>
+        <v>13.6000003814697</v>
       </c>
       <c r="E1997" t="n">
-        <v>14.0500001907349</v>
+        <v>13.8000001907349</v>
       </c>
       <c r="F1997" t="n">
-        <v>13.9499998092651</v>
+        <v>13.8000001907349</v>
       </c>
       <c r="G1997" t="s">
         <v>7</v>
@@ -46305,19 +46305,19 @@
     </row>
     <row r="1998">
       <c r="A1998" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1998" t="n">
-        <v>1999</v>
+        <v>2905</v>
       </c>
       <c r="C1998" t="n">
-        <v>14</v>
+        <v>14.1000003814697</v>
       </c>
       <c r="D1998" t="n">
-        <v>13.8000001907349</v>
+        <v>13.8999996185303</v>
       </c>
       <c r="E1998" t="n">
-        <v>14</v>
+        <v>14.0500001907349</v>
       </c>
       <c r="F1998" t="n">
         <v>13.9499998092651</v>
@@ -46328,22 +46328,22 @@
     </row>
     <row r="1999">
       <c r="A1999" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1999" t="n">
-        <v>1830</v>
+        <v>1999</v>
       </c>
       <c r="C1999" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1999" t="n">
         <v>13.8000001907349</v>
       </c>
-      <c r="D1999" t="n">
-        <v>13.6999998092651</v>
-      </c>
       <c r="E1999" t="n">
-        <v>13.8000001907349</v>
+        <v>14</v>
       </c>
       <c r="F1999" t="n">
-        <v>13.6999998092651</v>
+        <v>13.9499998092651</v>
       </c>
       <c r="G1999" t="s">
         <v>7</v>
@@ -46351,22 +46351,22 @@
     </row>
     <row r="2000">
       <c r="A2000" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2000" t="n">
-        <v>16747</v>
+        <v>1830</v>
       </c>
       <c r="C2000" t="n">
-        <v>14.1999998092651</v>
+        <v>13.8000001907349</v>
       </c>
       <c r="D2000" t="n">
         <v>13.6999998092651</v>
       </c>
       <c r="E2000" t="n">
-        <v>13.75</v>
+        <v>13.8000001907349</v>
       </c>
       <c r="F2000" t="n">
-        <v>14.1499996185303</v>
+        <v>13.6999998092651</v>
       </c>
       <c r="G2000" t="s">
         <v>7</v>
@@ -46374,22 +46374,22 @@
     </row>
     <row r="2001">
       <c r="A2001" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2001" t="n">
-        <v>3746</v>
+        <v>16747</v>
       </c>
       <c r="C2001" t="n">
-        <v>14.25</v>
+        <v>14.1999998092651</v>
       </c>
       <c r="D2001" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F2001" t="n">
         <v>14.1499996185303</v>
-      </c>
-      <c r="E2001" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="F2001" t="n">
-        <v>14.1999998092651</v>
       </c>
       <c r="G2001" t="s">
         <v>7</v>
@@ -46397,22 +46397,22 @@
     </row>
     <row r="2002">
       <c r="A2002" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2002" t="n">
-        <v>4031</v>
+        <v>3746</v>
       </c>
       <c r="C2002" t="n">
-        <v>14.4499998092651</v>
+        <v>14.25</v>
       </c>
       <c r="D2002" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="F2002" t="n">
         <v>14.1999998092651</v>
-      </c>
-      <c r="E2002" t="n">
-        <v>14.3000001907349</v>
-      </c>
-      <c r="F2002" t="n">
-        <v>14.3999996185303</v>
       </c>
       <c r="G2002" t="s">
         <v>7</v>
@@ -46420,24 +46420,47 @@
     </row>
     <row r="2003">
       <c r="A2003" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2003" t="n">
-        <v>3931</v>
+        <v>4031</v>
       </c>
       <c r="C2003" t="n">
-        <v>14.6499996185303</v>
+        <v>14.4499998092651</v>
       </c>
       <c r="D2003" t="n">
-        <v>14.1000003814697</v>
+        <v>14.1999998092651</v>
       </c>
       <c r="E2003" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="G2003" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2004" t="n">
+        <v>1285</v>
+      </c>
+      <c r="C2004" t="n">
         <v>14.6000003814697</v>
       </c>
-      <c r="F2003" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G2003" t="s">
+      <c r="D2004" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="G2004" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -52531,6 +52531,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2007">
+      <c r="A2007" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2007" t="n">
+        <v>5401</v>
+      </c>
+      <c r="C2007" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>15.0500001907349</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="H2007" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -52557,6 +52557,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2008">
+      <c r="A2008" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2008" t="n">
+        <v>2144</v>
+      </c>
+      <c r="C2008" t="n">
+        <v>15.3500003814697</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>15.3500003814697</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2008" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -52583,6 +52583,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2009">
+      <c r="A2009" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2009" t="n">
+        <v>2686</v>
+      </c>
+      <c r="C2009" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="G2009" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="H2009" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -52609,6 +52609,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2010">
+      <c r="A2010" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2010" t="n">
+        <v>4164</v>
+      </c>
+      <c r="C2010" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>14.6499996185303</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G2010" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="H2010" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -52687,6 +52687,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2013">
+      <c r="A2013" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2013" t="n">
+        <v>2390</v>
+      </c>
+      <c r="C2013" t="n">
+        <v>15.6999998092651</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>15.6999998092651</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>15.9499998092651</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>15.9499998092651</v>
+      </c>
+      <c r="H2013" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46733,8 +46733,31 @@
       <c r="E2016" t="n">
         <v>15.8999996185303</v>
       </c>
-      <c r="F2016"/>
+      <c r="F2016" t="n">
+        <v>16.0499992370605</v>
+      </c>
       <c r="G2016" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2017" t="n">
+        <v>4201</v>
+      </c>
+      <c r="C2017" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F2017"/>
+      <c r="G2017" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46756,8 +46756,31 @@
       <c r="E2017" t="n">
         <v>16.1000003814697</v>
       </c>
-      <c r="F2017"/>
+      <c r="F2017" t="n">
+        <v>17.3500003814697</v>
+      </c>
       <c r="G2017" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2018" t="n">
+        <v>4298</v>
+      </c>
+      <c r="C2018" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>16.7000007629395</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2018"/>
+      <c r="G2018" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46779,8 +46779,31 @@
       <c r="E2018" t="n">
         <v>17.5</v>
       </c>
-      <c r="F2018"/>
+      <c r="F2018" t="n">
+        <v>17.6000003814697</v>
+      </c>
       <c r="G2018" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2019" t="n">
+        <v>5408</v>
+      </c>
+      <c r="C2019" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>16.3500003814697</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="F2019"/>
+      <c r="G2019" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46802,8 +46802,31 @@
       <c r="E2019" t="n">
         <v>17.1499996185303</v>
       </c>
-      <c r="F2019"/>
+      <c r="F2019" t="n">
+        <v>16.7999992370605</v>
+      </c>
       <c r="G2019" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2020" t="n">
+        <v>3551</v>
+      </c>
+      <c r="C2020" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>16.9500007629395</v>
+      </c>
+      <c r="F2020"/>
+      <c r="G2020" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -46832,6 +46832,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2021">
+      <c r="A2021" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2021" t="n">
+        <v>1385</v>
+      </c>
+      <c r="C2021" t="n">
+        <v>16.5499992370605</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>16.1499996185303</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>16.5499992370605</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="G2021" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -52973,6 +52973,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2024">
+      <c r="A2024" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2024" t="n">
+        <v>1405</v>
+      </c>
+      <c r="C2024" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="H2024" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -52999,6 +52999,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2025">
+      <c r="A2025" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2025" t="n">
+        <v>835</v>
+      </c>
+      <c r="C2025" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>16.9500007629395</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="G2025" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="H2025" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59132,6 +59132,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2027">
+      <c r="A2027" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2027" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2027" t="n">
+        <v>17.5499992370605</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="E2027" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="G2027" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="H2027" t="n">
+        <v>2548</v>
+      </c>
+      <c r="I2027" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59155,9 +59155,38 @@
         <v>17.3999996185303</v>
       </c>
       <c r="H2027" t="n">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="I2027" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2028" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2028" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>17.3500003814697</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>17.3500003814697</v>
+      </c>
+      <c r="H2028" t="n">
+        <v>2160</v>
+      </c>
+      <c r="I2028" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59190,6 +59190,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2029">
+      <c r="A2029" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2029" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2029" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E2029" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="G2029" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="H2029" t="n">
+        <v>2501</v>
+      </c>
+      <c r="I2029" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59219,6 +59219,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2030">
+      <c r="A2030" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2030" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2030" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="E2030" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="G2030" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="H2030" t="n">
+        <v>5277</v>
+      </c>
+      <c r="I2030" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59248,6 +59248,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2031">
+      <c r="A2031" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2031" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2031" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="E2031" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="G2031" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="H2031" t="n">
+        <v>1098</v>
+      </c>
+      <c r="I2031" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59271,9 +59271,38 @@
         <v>18.3500003814697</v>
       </c>
       <c r="H2031" t="n">
-        <v>1098</v>
+        <v>1384</v>
       </c>
       <c r="I2031" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2032" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2032" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2032" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="G2032" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="H2032" t="n">
+        <v>1977</v>
+      </c>
+      <c r="I2032" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59306,6 +59306,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2033">
+      <c r="A2033" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2033" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2033" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="G2033" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="H2033" t="n">
+        <v>2932</v>
+      </c>
+      <c r="I2033" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59335,6 +59335,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2034">
+      <c r="A2034" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2034" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2034" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>18.8500003814697</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="G2034" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="H2034" t="n">
+        <v>1495</v>
+      </c>
+      <c r="I2034" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIRC.MI.xlsx
+++ b/data/CIRC.MI.xlsx
@@ -59364,6 +59364,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2035">
+      <c r="A2035" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2035" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2035" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="E2035" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>17.8500003814697</v>
+      </c>
+      <c r="G2035" t="n">
+        <v>17.8500003814697</v>
+      </c>
+      <c r="H2035" t="n">
+        <v>10377</v>
+      </c>
+      <c r="I2035" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
